--- a/assets/starter-pack/rebuilt/FLK_08_Price_to_Win_Worksheet.xlsx
+++ b/assets/starter-pack/rebuilt/FLK_08_Price_to_Win_Worksheet.xlsx
@@ -4,13 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Labor Benchmarks" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Cost Buildup" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Competitor Analysis" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Price-to-Win" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Labor Benchmarks" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Cost Buildup" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Competitor Analysis" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Price-to-Win" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="YesNo">Lists!$A$2:$A$3</definedName>
+    <definedName name="OdcCategory">Lists!$B$2:$B$7</definedName>
+    <definedName name="ClearanceLevel">Lists!$C$2:$C$7</definedName>
+    <definedName name="CompanySize">Lists!$D$2:$D$5</definedName>
+    <definedName name="SetAside">Lists!$E$2:$E$9</definedName>
+    <definedName name="EvalType">Lists!$F$2:$F$4,'Price-to-Win'!$C$5</definedName>
     <definedName name="BenchTable">'Labor Benchmarks'!$A$5:$G$34</definedName>
     <definedName name="BenchCategories">'Labor Benchmarks'!$A$5:$A$34</definedName>
     <definedName name="FringeRate">'Cost Buildup'!$B$5</definedName>
@@ -30,7 +37,6 @@
     <definedName name="CompMax">'Competitor Analysis'!$H$13</definedName>
     <definedName name="CompMedian">'Competitor Analysis'!$H$14</definedName>
     <definedName name="CompAvg">'Competitor Analysis'!$H$15</definedName>
-    <definedName name="EvalType">'Price-to-Win'!$C$5</definedName>
     <definedName name="YourTechScore">'Price-to-Win'!$C$6</definedName>
     <definedName name="CompTechScore">'Price-to-Win'!$C$7</definedName>
     <definedName name="TargetPWin">'Price-to-Win'!$C$8</definedName>
@@ -43,7 +49,112 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="244">
+  <si>
+    <t>Yes / No</t>
+  </si>
+  <si>
+    <t>ODC Category</t>
+  </si>
+  <si>
+    <t>Clearance Level</t>
+  </si>
+  <si>
+    <t>Company Size</t>
+  </si>
+  <si>
+    <t>Set-Aside Type</t>
+  </si>
+  <si>
+    <t>Evaluation Type</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Full &amp; Open</t>
+  </si>
+  <si>
+    <t>LPTA</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Public Trust</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Small Business</t>
+  </si>
+  <si>
+    <t>Best Value</t>
+  </si>
+  <si>
+    <t>Sub</t>
+  </si>
+  <si>
+    <t>Secret</t>
+  </si>
+  <si>
+    <t>Mid-Size</t>
+  </si>
+  <si>
+    <t>8(a)</t>
+  </si>
+  <si>
+    <t>Tradeoff</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Top Secret</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>HUBZone</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>TS/SCI</t>
+  </si>
+  <si>
+    <t>WOSB</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>TS/SCI w/ Poly</t>
+  </si>
+  <si>
+    <t>EDWOSB</t>
+  </si>
+  <si>
+    <t>SDVOSB</t>
+  </si>
+  <si>
+    <t>VOSB</t>
+  </si>
   <si>
     <t>FEDERAL LEAD KIT — Price-to-Win Worksheet</t>
   </si>
@@ -168,15 +279,9 @@
     <t>The price that wins the contract while preserving acceptable margin. Not the lowest price — the best-value price the customer expects to pay.</t>
   </si>
   <si>
-    <t>LPTA</t>
-  </si>
-  <si>
     <t>Lowest Price Technically Acceptable. The lowest compliant offer wins. PTW = the cost floor. Skip this RFP if your wrap is high.</t>
   </si>
   <si>
-    <t>Best Value</t>
-  </si>
-  <si>
     <t>Tradeoff between technical and price. You can win at a higher price if your past performance and approach justify it. Most federal services work uses this.</t>
   </si>
   <si>
@@ -243,21 +348,12 @@
     <t>Program Manager</t>
   </si>
   <si>
-    <t>Public Trust</t>
-  </si>
-  <si>
     <t>FY2026</t>
   </si>
   <si>
     <t>CALC + adj</t>
   </si>
   <si>
-    <t>Secret</t>
-  </si>
-  <si>
-    <t>TS/SCI</t>
-  </si>
-  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -438,27 +534,12 @@
     <t>Travel — CONUS trips</t>
   </si>
   <si>
-    <t>Travel</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Materials / hardware</t>
   </si>
   <si>
-    <t>Materials</t>
-  </si>
-  <si>
     <t>Subcontractor — Smith LLC</t>
   </si>
   <si>
-    <t>Sub</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>ODC TOTAL</t>
   </si>
   <si>
@@ -522,12 +603,6 @@
     <t>Lockheed Martin</t>
   </si>
   <si>
-    <t>Large</t>
-  </si>
-  <si>
-    <t>Full &amp; Open</t>
-  </si>
-  <si>
     <t>Incumbent on prior contract. Pulled from USASpending FY24 award.</t>
   </si>
   <si>
@@ -540,21 +615,12 @@
     <t>Mid-tier 8(a) firm</t>
   </si>
   <si>
-    <t>Small</t>
-  </si>
-  <si>
-    <t>8(a)</t>
-  </si>
-  <si>
     <t>Lower wrap due to smaller G&amp;A. Typical aggressive bid.</t>
   </si>
   <si>
     <t>Local SDVOSB</t>
   </si>
   <si>
-    <t>SDVOSB</t>
-  </si>
-  <si>
     <t>Won 2 of last 4 SDVOSB set-asides at this agency.</t>
   </si>
   <si>
@@ -586,9 +652,6 @@
   </si>
   <si>
     <t>EVALUATION + PRICING INPUTS</t>
-  </si>
-  <si>
-    <t>Evaluation Type</t>
   </si>
   <si>
     <t>Affects PTW logic</t>
@@ -730,12 +793,21 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -842,6 +914,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF047857"/>
       </patternFill>
     </fill>
@@ -853,11 +930,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -908,13 +980,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -922,133 +994,139 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1583,6 +1661,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF047857"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1596,245 +1811,245 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
+      <c r="A4" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>4</v>
+      <c r="B5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>6</v>
+      <c r="B6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>8</v>
+      <c r="B7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>10</v>
+      <c r="B8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
+      <c r="B9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
+      <c r="A11" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
+      <c r="B12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
+      <c r="B13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
+      <c r="B14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>21</v>
+      <c r="B15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>23</v>
+      <c r="B16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>24</v>
+      <c r="A18" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
     </row>
     <row r="19" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>26</v>
+      <c r="B19" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>28</v>
+      <c r="B20" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>30</v>
+      <c r="B21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>32</v>
+      <c r="B22" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>34</v>
+      <c r="B23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>36</v>
+      <c r="B24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>38</v>
+      <c r="B25" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>40</v>
+      <c r="B26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>42</v>
+      <c r="B27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>44</v>
+      <c r="B28" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>45</v>
+      <c r="A30" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="B30"/>
       <c r="C30"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>47</v>
+      <c r="B31" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>49</v>
+      <c r="B32" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>51</v>
+      <c r="B33" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>53</v>
+      <c r="B34" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>55</v>
+      <c r="B35" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +2070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
@@ -1870,8 +2085,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
+      <c r="A1" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -1881,8 +2096,8 @@
       <c r="G1"/>
     </row>
     <row r="2" ht="40" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>57</v>
+      <c r="A2" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -1892,716 +2107,716 @@
       <c r="G2"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="A4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="20">
+        <v>115</v>
+      </c>
+      <c r="D5" s="20">
+        <v>145</v>
+      </c>
+      <c r="E5" s="20">
+        <v>185</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="20">
+        <v>135</v>
+      </c>
+      <c r="D6" s="20">
+        <v>168</v>
+      </c>
+      <c r="E6" s="20">
+        <v>215</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="20">
+        <v>165</v>
+      </c>
+      <c r="D7" s="20">
+        <v>205</v>
+      </c>
+      <c r="E7" s="20">
+        <v>265</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="20">
+        <v>95</v>
+      </c>
+      <c r="D8" s="20">
+        <v>120</v>
+      </c>
+      <c r="E8" s="20">
+        <v>155</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="20">
+        <v>110</v>
+      </c>
+      <c r="D9" s="20">
+        <v>138</v>
+      </c>
+      <c r="E9" s="20">
+        <v>175</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="20">
+        <v>125</v>
+      </c>
+      <c r="D10" s="20">
+        <v>158</v>
+      </c>
+      <c r="E10" s="20">
+        <v>195</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="20">
+        <v>155</v>
+      </c>
+      <c r="D11" s="20">
+        <v>195</v>
+      </c>
+      <c r="E11" s="20">
+        <v>245</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="20">
+        <v>85</v>
+      </c>
+      <c r="D12" s="20">
+        <v>110</v>
+      </c>
+      <c r="E12" s="20">
+        <v>140</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="20">
+        <v>105</v>
+      </c>
+      <c r="D13" s="20">
+        <v>132</v>
+      </c>
+      <c r="E13" s="20">
+        <v>165</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="20">
+        <v>110</v>
+      </c>
+      <c r="D14" s="20">
+        <v>138</v>
+      </c>
+      <c r="E14" s="20">
+        <v>175</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="20">
+        <v>130</v>
+      </c>
+      <c r="D15" s="20">
+        <v>165</v>
+      </c>
+      <c r="E15" s="20">
+        <v>210</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="20">
+        <v>160</v>
+      </c>
+      <c r="D16" s="20">
+        <v>200</v>
+      </c>
+      <c r="E16" s="20">
+        <v>255</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="20">
+        <v>85</v>
+      </c>
+      <c r="D17" s="20">
+        <v>108</v>
+      </c>
+      <c r="E17" s="20">
+        <v>138</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="20">
+        <v>100</v>
+      </c>
+      <c r="D18" s="20">
+        <v>128</v>
+      </c>
+      <c r="E18" s="20">
+        <v>162</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="20">
+        <v>115</v>
+      </c>
+      <c r="D19" s="20">
+        <v>145</v>
+      </c>
+      <c r="E19" s="20">
+        <v>185</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="20">
+        <v>145</v>
+      </c>
+      <c r="D20" s="20">
+        <v>182</v>
+      </c>
+      <c r="E20" s="20">
+        <v>230</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="20">
+        <v>130</v>
+      </c>
+      <c r="D21" s="20">
+        <v>165</v>
+      </c>
+      <c r="E21" s="20">
+        <v>210</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="20">
+        <v>155</v>
+      </c>
+      <c r="D22" s="20">
+        <v>195</v>
+      </c>
+      <c r="E22" s="20">
+        <v>245</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="20">
+        <v>110</v>
+      </c>
+      <c r="D23" s="20">
+        <v>142</v>
+      </c>
+      <c r="E23" s="20">
+        <v>180</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="20">
+        <v>130</v>
+      </c>
+      <c r="D24" s="20">
+        <v>165</v>
+      </c>
+      <c r="E24" s="20">
+        <v>210</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="20">
+        <v>105</v>
+      </c>
+      <c r="D25" s="20">
+        <v>135</v>
+      </c>
+      <c r="E25" s="20">
+        <v>170</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="20">
+        <v>125</v>
+      </c>
+      <c r="D26" s="20">
+        <v>158</v>
+      </c>
+      <c r="E26" s="20">
+        <v>200</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="20">
+        <v>65</v>
+      </c>
+      <c r="D27" s="20">
+        <v>85</v>
+      </c>
+      <c r="E27" s="20">
+        <v>110</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="20">
+        <v>80</v>
+      </c>
+      <c r="D28" s="20">
+        <v>102</v>
+      </c>
+      <c r="E28" s="20">
+        <v>128</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="20">
+        <v>35</v>
+      </c>
+      <c r="D29" s="20">
+        <v>48</v>
+      </c>
+      <c r="E29" s="20">
         <v>62</v>
       </c>
-      <c r="F4" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="F29" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="20">
+        <v>48</v>
+      </c>
+      <c r="D30" s="20">
+        <v>62</v>
+      </c>
+      <c r="E30" s="20">
+        <v>78</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="20">
         <v>65</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="18">
-        <v>115</v>
-      </c>
-      <c r="D5" s="18">
-        <v>145</v>
-      </c>
-      <c r="E5" s="18">
-        <v>185</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="18">
-        <v>135</v>
-      </c>
-      <c r="D6" s="18">
-        <v>168</v>
-      </c>
-      <c r="E6" s="18">
-        <v>215</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="D31" s="20">
+        <v>82</v>
+      </c>
+      <c r="E31" s="20">
+        <v>105</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="20">
+        <v>28</v>
+      </c>
+      <c r="D32" s="20">
+        <v>38</v>
+      </c>
+      <c r="E32" s="20">
+        <v>50</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="20">
         <v>165</v>
       </c>
-      <c r="D7" s="18">
-        <v>205</v>
-      </c>
-      <c r="E7" s="18">
-        <v>265</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="18">
-        <v>95</v>
-      </c>
-      <c r="D8" s="18">
-        <v>120</v>
-      </c>
-      <c r="E8" s="18">
-        <v>155</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="18">
-        <v>110</v>
-      </c>
-      <c r="D9" s="18">
-        <v>138</v>
-      </c>
-      <c r="E9" s="18">
-        <v>175</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="18">
-        <v>125</v>
-      </c>
-      <c r="D10" s="18">
-        <v>158</v>
-      </c>
-      <c r="E10" s="18">
+      <c r="D33" s="20">
+        <v>210</v>
+      </c>
+      <c r="E33" s="20">
+        <v>275</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="20">
         <v>195</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="18">
-        <v>155</v>
-      </c>
-      <c r="D11" s="18">
-        <v>195</v>
-      </c>
-      <c r="E11" s="18">
-        <v>245</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="18">
-        <v>85</v>
-      </c>
-      <c r="D12" s="18">
-        <v>110</v>
-      </c>
-      <c r="E12" s="18">
-        <v>140</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="18">
-        <v>105</v>
-      </c>
-      <c r="D13" s="18">
-        <v>132</v>
-      </c>
-      <c r="E13" s="18">
-        <v>165</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="18">
-        <v>110</v>
-      </c>
-      <c r="D14" s="18">
-        <v>138</v>
-      </c>
-      <c r="E14" s="18">
-        <v>175</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="18">
-        <v>130</v>
-      </c>
-      <c r="D15" s="18">
-        <v>165</v>
-      </c>
-      <c r="E15" s="18">
-        <v>210</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="18">
-        <v>160</v>
-      </c>
-      <c r="D16" s="18">
-        <v>200</v>
-      </c>
-      <c r="E16" s="18">
-        <v>255</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="18">
-        <v>85</v>
-      </c>
-      <c r="D17" s="18">
-        <v>108</v>
-      </c>
-      <c r="E17" s="18">
-        <v>138</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="18">
-        <v>100</v>
-      </c>
-      <c r="D18" s="18">
-        <v>128</v>
-      </c>
-      <c r="E18" s="18">
-        <v>162</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="18">
-        <v>115</v>
-      </c>
-      <c r="D19" s="18">
-        <v>145</v>
-      </c>
-      <c r="E19" s="18">
-        <v>185</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="18">
-        <v>145</v>
-      </c>
-      <c r="D20" s="18">
-        <v>182</v>
-      </c>
-      <c r="E20" s="18">
-        <v>230</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="18">
-        <v>130</v>
-      </c>
-      <c r="D21" s="18">
-        <v>165</v>
-      </c>
-      <c r="E21" s="18">
-        <v>210</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="17" t="s">
+      <c r="D34" s="20">
+        <v>250</v>
+      </c>
+      <c r="E34" s="20">
+        <v>325</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" s="19" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="18">
-        <v>155</v>
-      </c>
-      <c r="D22" s="18">
-        <v>195</v>
-      </c>
-      <c r="E22" s="18">
-        <v>245</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="18">
-        <v>110</v>
-      </c>
-      <c r="D23" s="18">
-        <v>142</v>
-      </c>
-      <c r="E23" s="18">
-        <v>180</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="18">
-        <v>130</v>
-      </c>
-      <c r="D24" s="18">
-        <v>165</v>
-      </c>
-      <c r="E24" s="18">
-        <v>210</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="18">
-        <v>105</v>
-      </c>
-      <c r="D25" s="18">
-        <v>135</v>
-      </c>
-      <c r="E25" s="18">
-        <v>170</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="18">
-        <v>125</v>
-      </c>
-      <c r="D26" s="18">
-        <v>158</v>
-      </c>
-      <c r="E26" s="18">
-        <v>200</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="18">
-        <v>65</v>
-      </c>
-      <c r="D27" s="18">
-        <v>85</v>
-      </c>
-      <c r="E27" s="18">
-        <v>110</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="18">
-        <v>80</v>
-      </c>
-      <c r="D28" s="18">
-        <v>102</v>
-      </c>
-      <c r="E28" s="18">
-        <v>128</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="18">
-        <v>35</v>
-      </c>
-      <c r="D29" s="18">
-        <v>48</v>
-      </c>
-      <c r="E29" s="18">
-        <v>62</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="18">
-        <v>48</v>
-      </c>
-      <c r="D30" s="18">
-        <v>62</v>
-      </c>
-      <c r="E30" s="18">
-        <v>78</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="18">
-        <v>65</v>
-      </c>
-      <c r="D31" s="18">
-        <v>82</v>
-      </c>
-      <c r="E31" s="18">
-        <v>105</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="18">
-        <v>28</v>
-      </c>
-      <c r="D32" s="18">
-        <v>38</v>
-      </c>
-      <c r="E32" s="18">
-        <v>50</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="18">
-        <v>165</v>
-      </c>
-      <c r="D33" s="18">
-        <v>210</v>
-      </c>
-      <c r="E33" s="18">
-        <v>275</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="18">
-        <v>195</v>
-      </c>
-      <c r="D34" s="18">
-        <v>250</v>
-      </c>
-      <c r="E34" s="18">
-        <v>325</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2618,7 +2833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
@@ -2635,8 +2850,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>89</v>
+      <c r="A1" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -2654,8 +2869,8 @@
       <c r="O1"/>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>90</v>
+      <c r="A2" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -2673,8 +2888,8 @@
       <c r="O2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>91</v>
+      <c r="A4" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -2692,100 +2907,100 @@
       <c r="O4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="19">
+      <c r="A5" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="21">
         <v>0.3</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>93</v>
+      <c r="C5" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="A6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="21">
         <v>0.18</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>95</v>
+      <c r="C6" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="19">
+      <c r="A7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="21">
         <v>0.12</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>97</v>
+      <c r="C7" s="22" t="s">
+        <v>127</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="19">
+      <c r="A8" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="21">
         <v>0.08</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>99</v>
+      <c r="C8" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="21">
+      <c r="A9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="23">
         <f>(1+FringeRate)*(1+OHRate)*(1+GARate)</f>
       </c>
-      <c r="C9" s="22" t="s">
-        <v>101</v>
+      <c r="C9" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="21">
+      <c r="A10" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="23">
         <f>WrapRate*(1+FeeRate)</f>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>103</v>
+      <c r="C10" s="24" t="s">
+        <v>133</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="23">
+      <c r="A11" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="25">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>105</v>
+      <c r="A13" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -2803,660 +3018,660 @@
       <c r="O13"/>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="A14" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="O14" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="25">
+        <v>1</v>
+      </c>
+      <c r="D15" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E15" s="29">
+        <f>IF(OR(C15="",D15=""),"",C15*D15*PoPYears)</f>
+      </c>
+      <c r="F15" s="30">
+        <v>165</v>
+      </c>
+      <c r="G15" s="31">
+        <f>IF(F15="","",F15*(1+FringeRate))</f>
+      </c>
+      <c r="H15" s="31">
+        <f>IF(G15="","",G15*(1+OHRate))</f>
+      </c>
+      <c r="I15" s="31">
+        <f>IF(H15="","",H15*(1+GARate))</f>
+      </c>
+      <c r="J15" s="32">
+        <f>IF(I15="","",I15)</f>
+      </c>
+      <c r="K15" s="33">
+        <f>IF(OR(E15="",J15=""),"",E15*J15)</f>
+      </c>
+      <c r="L15" s="32">
+        <f>IF(J15="","",J15*(1+FeeRate))</f>
+      </c>
+      <c r="M15" s="33">
+        <f>IF(OR(E15="",L15=""),"",E15*L15)</f>
+      </c>
+      <c r="N15" s="20">
+        <f>IFERROR(VLOOKUP(A15,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O15" s="34">
+        <f>IF(OR(N15="",L15=""),"",(L15-N15)/N15)</f>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="25">
+        <v>2</v>
+      </c>
+      <c r="D16" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E16" s="29">
+        <f>IF(OR(C16="",D16=""),"",C16*D16*PoPYears)</f>
+      </c>
+      <c r="F16" s="30">
+        <v>145</v>
+      </c>
+      <c r="G16" s="31">
+        <f>IF(F16="","",F16*(1+FringeRate))</f>
+      </c>
+      <c r="H16" s="31">
+        <f>IF(G16="","",G16*(1+OHRate))</f>
+      </c>
+      <c r="I16" s="31">
+        <f>IF(H16="","",H16*(1+GARate))</f>
+      </c>
+      <c r="J16" s="32">
+        <f>IF(I16="","",I16)</f>
+      </c>
+      <c r="K16" s="33">
+        <f>IF(OR(E16="",J16=""),"",E16*J16)</f>
+      </c>
+      <c r="L16" s="32">
+        <f>IF(J16="","",J16*(1+FeeRate))</f>
+      </c>
+      <c r="M16" s="33">
+        <f>IF(OR(E16="",L16=""),"",E16*L16)</f>
+      </c>
+      <c r="N16" s="20">
+        <f>IFERROR(VLOOKUP(A16,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O16" s="34">
+        <f>IF(OR(N16="",L16=""),"",(L16-N16)/N16)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="25">
+        <v>3</v>
+      </c>
+      <c r="D17" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E17" s="29">
+        <f>IF(OR(C17="",D17=""),"",C17*D17*PoPYears)</f>
+      </c>
+      <c r="F17" s="30">
+        <v>105</v>
+      </c>
+      <c r="G17" s="31">
+        <f>IF(F17="","",F17*(1+FringeRate))</f>
+      </c>
+      <c r="H17" s="31">
+        <f>IF(G17="","",G17*(1+OHRate))</f>
+      </c>
+      <c r="I17" s="31">
+        <f>IF(H17="","",H17*(1+GARate))</f>
+      </c>
+      <c r="J17" s="32">
+        <f>IF(I17="","",I17)</f>
+      </c>
+      <c r="K17" s="33">
+        <f>IF(OR(E17="",J17=""),"",E17*J17)</f>
+      </c>
+      <c r="L17" s="32">
+        <f>IF(J17="","",J17*(1+FeeRate))</f>
+      </c>
+      <c r="M17" s="33">
+        <f>IF(OR(E17="",L17=""),"",E17*L17)</f>
+      </c>
+      <c r="N17" s="20">
+        <f>IFERROR(VLOOKUP(A17,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O17" s="34">
+        <f>IF(OR(N17="",L17=""),"",(L17-N17)/N17)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="25">
+        <v>2</v>
+      </c>
+      <c r="D18" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E18" s="29">
+        <f>IF(OR(C18="",D18=""),"",C18*D18*PoPYears)</f>
+      </c>
+      <c r="F18" s="30">
+        <v>130</v>
+      </c>
+      <c r="G18" s="31">
+        <f>IF(F18="","",F18*(1+FringeRate))</f>
+      </c>
+      <c r="H18" s="31">
+        <f>IF(G18="","",G18*(1+OHRate))</f>
+      </c>
+      <c r="I18" s="31">
+        <f>IF(H18="","",H18*(1+GARate))</f>
+      </c>
+      <c r="J18" s="32">
+        <f>IF(I18="","",I18)</f>
+      </c>
+      <c r="K18" s="33">
+        <f>IF(OR(E18="",J18=""),"",E18*J18)</f>
+      </c>
+      <c r="L18" s="32">
+        <f>IF(J18="","",J18*(1+FeeRate))</f>
+      </c>
+      <c r="M18" s="33">
+        <f>IF(OR(E18="",L18=""),"",E18*L18)</f>
+      </c>
+      <c r="N18" s="20">
+        <f>IFERROR(VLOOKUP(A18,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O18" s="34">
+        <f>IF(OR(N18="",L18=""),"",(L18-N18)/N18)</f>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="B19" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="25">
+        <v>2</v>
+      </c>
+      <c r="D19" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E19" s="29">
+        <f>IF(OR(C19="",D19=""),"",C19*D19*PoPYears)</f>
+      </c>
+      <c r="F19" s="30">
+        <v>95</v>
+      </c>
+      <c r="G19" s="31">
+        <f>IF(F19="","",F19*(1+FringeRate))</f>
+      </c>
+      <c r="H19" s="31">
+        <f>IF(G19="","",G19*(1+OHRate))</f>
+      </c>
+      <c r="I19" s="31">
+        <f>IF(H19="","",H19*(1+GARate))</f>
+      </c>
+      <c r="J19" s="32">
+        <f>IF(I19="","",I19)</f>
+      </c>
+      <c r="K19" s="33">
+        <f>IF(OR(E19="",J19=""),"",E19*J19)</f>
+      </c>
+      <c r="L19" s="32">
+        <f>IF(J19="","",J19*(1+FeeRate))</f>
+      </c>
+      <c r="M19" s="33">
+        <f>IF(OR(E19="",L19=""),"",E19*L19)</f>
+      </c>
+      <c r="N19" s="20">
+        <f>IFERROR(VLOOKUP(A19,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O19" s="34">
+        <f>IF(OR(N19="",L19=""),"",(L19-N19)/N19)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" s="15" t="s">
+      <c r="B20" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="25">
+        <v>1</v>
+      </c>
+      <c r="D20" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E20" s="29">
+        <f>IF(OR(C20="",D20=""),"",C20*D20*PoPYears)</f>
+      </c>
+      <c r="F20" s="30">
+        <v>115</v>
+      </c>
+      <c r="G20" s="31">
+        <f>IF(F20="","",F20*(1+FringeRate))</f>
+      </c>
+      <c r="H20" s="31">
+        <f>IF(G20="","",G20*(1+OHRate))</f>
+      </c>
+      <c r="I20" s="31">
+        <f>IF(H20="","",H20*(1+GARate))</f>
+      </c>
+      <c r="J20" s="32">
+        <f>IF(I20="","",I20)</f>
+      </c>
+      <c r="K20" s="33">
+        <f>IF(OR(E20="",J20=""),"",E20*J20)</f>
+      </c>
+      <c r="L20" s="32">
+        <f>IF(J20="","",J20*(1+FeeRate))</f>
+      </c>
+      <c r="M20" s="33">
+        <f>IF(OR(E20="",L20=""),"",E20*L20)</f>
+      </c>
+      <c r="N20" s="20">
+        <f>IFERROR(VLOOKUP(A20,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O20" s="34">
+        <f>IF(OR(N20="",L20=""),"",(L20-N20)/N20)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="B21" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="25">
+        <v>1</v>
+      </c>
+      <c r="D21" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E21" s="29">
+        <f>IF(OR(C21="",D21=""),"",C21*D21*PoPYears)</f>
+      </c>
+      <c r="F21" s="30">
+        <v>105</v>
+      </c>
+      <c r="G21" s="31">
+        <f>IF(F21="","",F21*(1+FringeRate))</f>
+      </c>
+      <c r="H21" s="31">
+        <f>IF(G21="","",G21*(1+OHRate))</f>
+      </c>
+      <c r="I21" s="31">
+        <f>IF(H21="","",H21*(1+GARate))</f>
+      </c>
+      <c r="J21" s="32">
+        <f>IF(I21="","",I21)</f>
+      </c>
+      <c r="K21" s="33">
+        <f>IF(OR(E21="",J21=""),"",E21*J21)</f>
+      </c>
+      <c r="L21" s="32">
+        <f>IF(J21="","",J21*(1+FeeRate))</f>
+      </c>
+      <c r="M21" s="33">
+        <f>IF(OR(E21="",L21=""),"",E21*L21)</f>
+      </c>
+      <c r="N21" s="20">
+        <f>IFERROR(VLOOKUP(A21,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O21" s="34">
+        <f>IF(OR(N21="",L21=""),"",(L21-N21)/N21)</f>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="B22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="25">
+        <v>1</v>
+      </c>
+      <c r="D22" s="28">
+        <v>1880</v>
+      </c>
+      <c r="E22" s="29">
+        <f>IF(OR(C22="",D22=""),"",C22*D22*PoPYears)</f>
+      </c>
+      <c r="F22" s="30">
         <v>65</v>
       </c>
-      <c r="B15" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23">
-        <v>1</v>
-      </c>
-      <c r="D15" s="26">
+      <c r="G22" s="31">
+        <f>IF(F22="","",F22*(1+FringeRate))</f>
+      </c>
+      <c r="H22" s="31">
+        <f>IF(G22="","",G22*(1+OHRate))</f>
+      </c>
+      <c r="I22" s="31">
+        <f>IF(H22="","",H22*(1+GARate))</f>
+      </c>
+      <c r="J22" s="32">
+        <f>IF(I22="","",I22)</f>
+      </c>
+      <c r="K22" s="33">
+        <f>IF(OR(E22="",J22=""),"",E22*J22)</f>
+      </c>
+      <c r="L22" s="32">
+        <f>IF(J22="","",J22*(1+FeeRate))</f>
+      </c>
+      <c r="M22" s="33">
+        <f>IF(OR(E22="",L22=""),"",E22*L22)</f>
+      </c>
+      <c r="N22" s="20">
+        <f>IFERROR(VLOOKUP(A22,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O22" s="34">
+        <f>IF(OR(N22="",L22=""),"",(L22-N22)/N22)</f>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="28">
         <v>1880</v>
       </c>
-      <c r="E15" s="27">
-        <f>IF(OR(C15="",D15=""),"",C15*D15*PoPYears)</f>
-      </c>
-      <c r="F15" s="28">
-        <v>165</v>
-      </c>
-      <c r="G15" s="29">
-        <f>IF(F15="","",F15*(1+FringeRate))</f>
-      </c>
-      <c r="H15" s="29">
-        <f>IF(G15="","",G15*(1+OHRate))</f>
-      </c>
-      <c r="I15" s="29">
-        <f>IF(H15="","",H15*(1+GARate))</f>
-      </c>
-      <c r="J15" s="30">
-        <f>IF(I15="","",I15)</f>
-      </c>
-      <c r="K15" s="31">
-        <f>IF(OR(E15="",J15=""),"",E15*J15)</f>
-      </c>
-      <c r="L15" s="30">
-        <f>IF(J15="","",J15*(1+FeeRate))</f>
-      </c>
-      <c r="M15" s="31">
-        <f>IF(OR(E15="",L15=""),"",E15*L15)</f>
-      </c>
-      <c r="N15" s="18">
-        <f>IFERROR(VLOOKUP(A15,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O15" s="32">
-        <f>IF(OR(N15="",L15=""),"",(L15-N15)/N15)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="23">
-        <v>2</v>
-      </c>
-      <c r="D16" s="26">
+      <c r="E23" s="29">
+        <f>IF(OR(C23="",D23=""),"",C23*D23*PoPYears)</f>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="31">
+        <f>IF(F23="","",F23*(1+FringeRate))</f>
+      </c>
+      <c r="H23" s="31">
+        <f>IF(G23="","",G23*(1+OHRate))</f>
+      </c>
+      <c r="I23" s="31">
+        <f>IF(H23="","",H23*(1+GARate))</f>
+      </c>
+      <c r="J23" s="32">
+        <f>IF(I23="","",I23)</f>
+      </c>
+      <c r="K23" s="33">
+        <f>IF(OR(E23="",J23=""),"",E23*J23)</f>
+      </c>
+      <c r="L23" s="32">
+        <f>IF(J23="","",J23*(1+FeeRate))</f>
+      </c>
+      <c r="M23" s="33">
+        <f>IF(OR(E23="",L23=""),"",E23*L23)</f>
+      </c>
+      <c r="N23" s="20">
+        <f>IFERROR(VLOOKUP(A23,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O23" s="34">
+        <f>IF(OR(N23="",L23=""),"",(L23-N23)/N23)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="28">
         <v>1880</v>
       </c>
-      <c r="E16" s="27">
-        <f>IF(OR(C16="",D16=""),"",C16*D16*PoPYears)</f>
-      </c>
-      <c r="F16" s="28">
-        <v>145</v>
-      </c>
-      <c r="G16" s="29">
-        <f>IF(F16="","",F16*(1+FringeRate))</f>
-      </c>
-      <c r="H16" s="29">
-        <f>IF(G16="","",G16*(1+OHRate))</f>
-      </c>
-      <c r="I16" s="29">
-        <f>IF(H16="","",H16*(1+GARate))</f>
-      </c>
-      <c r="J16" s="30">
-        <f>IF(I16="","",I16)</f>
-      </c>
-      <c r="K16" s="31">
-        <f>IF(OR(E16="",J16=""),"",E16*J16)</f>
-      </c>
-      <c r="L16" s="30">
-        <f>IF(J16="","",J16*(1+FeeRate))</f>
-      </c>
-      <c r="M16" s="31">
-        <f>IF(OR(E16="",L16=""),"",E16*L16)</f>
-      </c>
-      <c r="N16" s="18">
-        <f>IFERROR(VLOOKUP(A16,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O16" s="32">
-        <f>IF(OR(N16="",L16=""),"",(L16-N16)/N16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23">
-        <v>3</v>
-      </c>
-      <c r="D17" s="26">
+      <c r="E24" s="29">
+        <f>IF(OR(C24="",D24=""),"",C24*D24*PoPYears)</f>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="31">
+        <f>IF(F24="","",F24*(1+FringeRate))</f>
+      </c>
+      <c r="H24" s="31">
+        <f>IF(G24="","",G24*(1+OHRate))</f>
+      </c>
+      <c r="I24" s="31">
+        <f>IF(H24="","",H24*(1+GARate))</f>
+      </c>
+      <c r="J24" s="32">
+        <f>IF(I24="","",I24)</f>
+      </c>
+      <c r="K24" s="33">
+        <f>IF(OR(E24="",J24=""),"",E24*J24)</f>
+      </c>
+      <c r="L24" s="32">
+        <f>IF(J24="","",J24*(1+FeeRate))</f>
+      </c>
+      <c r="M24" s="33">
+        <f>IF(OR(E24="",L24=""),"",E24*L24)</f>
+      </c>
+      <c r="N24" s="20">
+        <f>IFERROR(VLOOKUP(A24,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O24" s="34">
+        <f>IF(OR(N24="",L24=""),"",(L24-N24)/N24)</f>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="28">
         <v>1880</v>
       </c>
-      <c r="E17" s="27">
-        <f>IF(OR(C17="",D17=""),"",C17*D17*PoPYears)</f>
-      </c>
-      <c r="F17" s="28">
-        <v>105</v>
-      </c>
-      <c r="G17" s="29">
-        <f>IF(F17="","",F17*(1+FringeRate))</f>
-      </c>
-      <c r="H17" s="29">
-        <f>IF(G17="","",G17*(1+OHRate))</f>
-      </c>
-      <c r="I17" s="29">
-        <f>IF(H17="","",H17*(1+GARate))</f>
-      </c>
-      <c r="J17" s="30">
-        <f>IF(I17="","",I17)</f>
-      </c>
-      <c r="K17" s="31">
-        <f>IF(OR(E17="",J17=""),"",E17*J17)</f>
-      </c>
-      <c r="L17" s="30">
-        <f>IF(J17="","",J17*(1+FeeRate))</f>
-      </c>
-      <c r="M17" s="31">
-        <f>IF(OR(E17="",L17=""),"",E17*L17)</f>
-      </c>
-      <c r="N17" s="18">
-        <f>IFERROR(VLOOKUP(A17,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O17" s="32">
-        <f>IF(OR(N17="",L17=""),"",(L17-N17)/N17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23">
-        <v>2</v>
-      </c>
-      <c r="D18" s="26">
+      <c r="E25" s="29">
+        <f>IF(OR(C25="",D25=""),"",C25*D25*PoPYears)</f>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="31">
+        <f>IF(F25="","",F25*(1+FringeRate))</f>
+      </c>
+      <c r="H25" s="31">
+        <f>IF(G25="","",G25*(1+OHRate))</f>
+      </c>
+      <c r="I25" s="31">
+        <f>IF(H25="","",H25*(1+GARate))</f>
+      </c>
+      <c r="J25" s="32">
+        <f>IF(I25="","",I25)</f>
+      </c>
+      <c r="K25" s="33">
+        <f>IF(OR(E25="",J25=""),"",E25*J25)</f>
+      </c>
+      <c r="L25" s="32">
+        <f>IF(J25="","",J25*(1+FeeRate))</f>
+      </c>
+      <c r="M25" s="33">
+        <f>IF(OR(E25="",L25=""),"",E25*L25)</f>
+      </c>
+      <c r="N25" s="20">
+        <f>IFERROR(VLOOKUP(A25,BenchTable,4,FALSE),"")</f>
+      </c>
+      <c r="O25" s="34">
+        <f>IF(OR(N25="",L25=""),"",(L25-N25)/N25)</f>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="28">
         <v>1880</v>
       </c>
-      <c r="E18" s="27">
-        <f>IF(OR(C18="",D18=""),"",C18*D18*PoPYears)</f>
-      </c>
-      <c r="F18" s="28">
-        <v>130</v>
-      </c>
-      <c r="G18" s="29">
-        <f>IF(F18="","",F18*(1+FringeRate))</f>
-      </c>
-      <c r="H18" s="29">
-        <f>IF(G18="","",G18*(1+OHRate))</f>
-      </c>
-      <c r="I18" s="29">
-        <f>IF(H18="","",H18*(1+GARate))</f>
-      </c>
-      <c r="J18" s="30">
-        <f>IF(I18="","",I18)</f>
-      </c>
-      <c r="K18" s="31">
-        <f>IF(OR(E18="",J18=""),"",E18*J18)</f>
-      </c>
-      <c r="L18" s="30">
-        <f>IF(J18="","",J18*(1+FeeRate))</f>
-      </c>
-      <c r="M18" s="31">
-        <f>IF(OR(E18="",L18=""),"",E18*L18)</f>
-      </c>
-      <c r="N18" s="18">
-        <f>IFERROR(VLOOKUP(A18,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O18" s="32">
-        <f>IF(OR(N18="",L18=""),"",(L18-N18)/N18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="23">
-        <v>2</v>
-      </c>
-      <c r="D19" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E19" s="27">
-        <f>IF(OR(C19="",D19=""),"",C19*D19*PoPYears)</f>
-      </c>
-      <c r="F19" s="28">
-        <v>95</v>
-      </c>
-      <c r="G19" s="29">
-        <f>IF(F19="","",F19*(1+FringeRate))</f>
-      </c>
-      <c r="H19" s="29">
-        <f>IF(G19="","",G19*(1+OHRate))</f>
-      </c>
-      <c r="I19" s="29">
-        <f>IF(H19="","",H19*(1+GARate))</f>
-      </c>
-      <c r="J19" s="30">
-        <f>IF(I19="","",I19)</f>
-      </c>
-      <c r="K19" s="31">
-        <f>IF(OR(E19="",J19=""),"",E19*J19)</f>
-      </c>
-      <c r="L19" s="30">
-        <f>IF(J19="","",J19*(1+FeeRate))</f>
-      </c>
-      <c r="M19" s="31">
-        <f>IF(OR(E19="",L19=""),"",E19*L19)</f>
-      </c>
-      <c r="N19" s="18">
-        <f>IFERROR(VLOOKUP(A19,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O19" s="32">
-        <f>IF(OR(N19="",L19=""),"",(L19-N19)/N19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="23">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E20" s="27">
-        <f>IF(OR(C20="",D20=""),"",C20*D20*PoPYears)</f>
-      </c>
-      <c r="F20" s="28">
-        <v>115</v>
-      </c>
-      <c r="G20" s="29">
-        <f>IF(F20="","",F20*(1+FringeRate))</f>
-      </c>
-      <c r="H20" s="29">
-        <f>IF(G20="","",G20*(1+OHRate))</f>
-      </c>
-      <c r="I20" s="29">
-        <f>IF(H20="","",H20*(1+GARate))</f>
-      </c>
-      <c r="J20" s="30">
-        <f>IF(I20="","",I20)</f>
-      </c>
-      <c r="K20" s="31">
-        <f>IF(OR(E20="",J20=""),"",E20*J20)</f>
-      </c>
-      <c r="L20" s="30">
-        <f>IF(J20="","",J20*(1+FeeRate))</f>
-      </c>
-      <c r="M20" s="31">
-        <f>IF(OR(E20="",L20=""),"",E20*L20)</f>
-      </c>
-      <c r="N20" s="18">
-        <f>IFERROR(VLOOKUP(A20,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O20" s="32">
-        <f>IF(OR(N20="",L20=""),"",(L20-N20)/N20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="23">
-        <v>1</v>
-      </c>
-      <c r="D21" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E21" s="27">
-        <f>IF(OR(C21="",D21=""),"",C21*D21*PoPYears)</f>
-      </c>
-      <c r="F21" s="28">
-        <v>105</v>
-      </c>
-      <c r="G21" s="29">
-        <f>IF(F21="","",F21*(1+FringeRate))</f>
-      </c>
-      <c r="H21" s="29">
-        <f>IF(G21="","",G21*(1+OHRate))</f>
-      </c>
-      <c r="I21" s="29">
-        <f>IF(H21="","",H21*(1+GARate))</f>
-      </c>
-      <c r="J21" s="30">
-        <f>IF(I21="","",I21)</f>
-      </c>
-      <c r="K21" s="31">
-        <f>IF(OR(E21="",J21=""),"",E21*J21)</f>
-      </c>
-      <c r="L21" s="30">
-        <f>IF(J21="","",J21*(1+FeeRate))</f>
-      </c>
-      <c r="M21" s="31">
-        <f>IF(OR(E21="",L21=""),"",E21*L21)</f>
-      </c>
-      <c r="N21" s="18">
-        <f>IFERROR(VLOOKUP(A21,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O21" s="32">
-        <f>IF(OR(N21="",L21=""),"",(L21-N21)/N21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="23">
-        <v>1</v>
-      </c>
-      <c r="D22" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E22" s="27">
-        <f>IF(OR(C22="",D22=""),"",C22*D22*PoPYears)</f>
-      </c>
-      <c r="F22" s="28">
-        <v>65</v>
-      </c>
-      <c r="G22" s="29">
-        <f>IF(F22="","",F22*(1+FringeRate))</f>
-      </c>
-      <c r="H22" s="29">
-        <f>IF(G22="","",G22*(1+OHRate))</f>
-      </c>
-      <c r="I22" s="29">
-        <f>IF(H22="","",H22*(1+GARate))</f>
-      </c>
-      <c r="J22" s="30">
-        <f>IF(I22="","",I22)</f>
-      </c>
-      <c r="K22" s="31">
-        <f>IF(OR(E22="",J22=""),"",E22*J22)</f>
-      </c>
-      <c r="L22" s="30">
-        <f>IF(J22="","",J22*(1+FeeRate))</f>
-      </c>
-      <c r="M22" s="31">
-        <f>IF(OR(E22="",L22=""),"",E22*L22)</f>
-      </c>
-      <c r="N22" s="18">
-        <f>IFERROR(VLOOKUP(A22,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O22" s="32">
-        <f>IF(OR(N22="",L22=""),"",(L22-N22)/N22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E23" s="27">
-        <f>IF(OR(C23="",D23=""),"",C23*D23*PoPYears)</f>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="29">
-        <f>IF(F23="","",F23*(1+FringeRate))</f>
-      </c>
-      <c r="H23" s="29">
-        <f>IF(G23="","",G23*(1+OHRate))</f>
-      </c>
-      <c r="I23" s="29">
-        <f>IF(H23="","",H23*(1+GARate))</f>
-      </c>
-      <c r="J23" s="30">
-        <f>IF(I23="","",I23)</f>
-      </c>
-      <c r="K23" s="31">
-        <f>IF(OR(E23="",J23=""),"",E23*J23)</f>
-      </c>
-      <c r="L23" s="30">
-        <f>IF(J23="","",J23*(1+FeeRate))</f>
-      </c>
-      <c r="M23" s="31">
-        <f>IF(OR(E23="",L23=""),"",E23*L23)</f>
-      </c>
-      <c r="N23" s="18">
-        <f>IFERROR(VLOOKUP(A23,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O23" s="32">
-        <f>IF(OR(N23="",L23=""),"",(L23-N23)/N23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E24" s="27">
-        <f>IF(OR(C24="",D24=""),"",C24*D24*PoPYears)</f>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="29">
-        <f>IF(F24="","",F24*(1+FringeRate))</f>
-      </c>
-      <c r="H24" s="29">
-        <f>IF(G24="","",G24*(1+OHRate))</f>
-      </c>
-      <c r="I24" s="29">
-        <f>IF(H24="","",H24*(1+GARate))</f>
-      </c>
-      <c r="J24" s="30">
-        <f>IF(I24="","",I24)</f>
-      </c>
-      <c r="K24" s="31">
-        <f>IF(OR(E24="",J24=""),"",E24*J24)</f>
-      </c>
-      <c r="L24" s="30">
-        <f>IF(J24="","",J24*(1+FeeRate))</f>
-      </c>
-      <c r="M24" s="31">
-        <f>IF(OR(E24="",L24=""),"",E24*L24)</f>
-      </c>
-      <c r="N24" s="18">
-        <f>IFERROR(VLOOKUP(A24,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O24" s="32">
-        <f>IF(OR(N24="",L24=""),"",(L24-N24)/N24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E25" s="27">
-        <f>IF(OR(C25="",D25=""),"",C25*D25*PoPYears)</f>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" s="29">
-        <f>IF(F25="","",F25*(1+FringeRate))</f>
-      </c>
-      <c r="H25" s="29">
-        <f>IF(G25="","",G25*(1+OHRate))</f>
-      </c>
-      <c r="I25" s="29">
-        <f>IF(H25="","",H25*(1+GARate))</f>
-      </c>
-      <c r="J25" s="30">
-        <f>IF(I25="","",I25)</f>
-      </c>
-      <c r="K25" s="31">
-        <f>IF(OR(E25="",J25=""),"",E25*J25)</f>
-      </c>
-      <c r="L25" s="30">
-        <f>IF(J25="","",J25*(1+FeeRate))</f>
-      </c>
-      <c r="M25" s="31">
-        <f>IF(OR(E25="",L25=""),"",E25*L25)</f>
-      </c>
-      <c r="N25" s="18">
-        <f>IFERROR(VLOOKUP(A25,BenchTable,4,FALSE),"")</f>
-      </c>
-      <c r="O25" s="32">
-        <f>IF(OR(N25="",L25=""),"",(L25-N25)/N25)</f>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="26">
-        <v>1880</v>
-      </c>
-      <c r="E26" s="27">
+      <c r="E26" s="29">
         <f>IF(OR(C26="",D26=""),"",C26*D26*PoPYears)</f>
       </c>
-      <c r="F26" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G26" s="29">
+      <c r="F26" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" s="31">
         <f>IF(F26="","",F26*(1+FringeRate))</f>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="31">
         <f>IF(G26="","",G26*(1+OHRate))</f>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="31">
         <f>IF(H26="","",H26*(1+GARate))</f>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="32">
         <f>IF(I26="","",I26)</f>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="33">
         <f>IF(OR(E26="",J26=""),"",E26*J26)</f>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="32">
         <f>IF(J26="","",J26*(1+FeeRate))</f>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="33">
         <f>IF(OR(E26="",L26=""),"",E26*L26)</f>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="20">
         <f>IFERROR(VLOOKUP(A26,BenchTable,4,FALSE),"")</f>
       </c>
-      <c r="O26" s="32">
+      <c r="O26" s="34">
         <f>IF(OR(N26="",L26=""),"",(L26-N26)/N26)</f>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="34">
+      <c r="A27" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36">
         <f>SUM(E15:E26)</f>
       </c>
-      <c r="F27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="J27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="K27" s="36">
+      <c r="F27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="K27" s="38">
         <f>SUM(K15:K26)</f>
       </c>
-      <c r="L27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="M27" s="36">
+      <c r="L27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="M27" s="38">
         <f>SUM(M15:M26)</f>
       </c>
-      <c r="N27" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O27" s="35" t="s">
-        <v>119</v>
+      <c r="N27" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="O27" s="37" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>121</v>
+      <c r="A29" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
@@ -3474,187 +3689,187 @@
       <c r="O29"/>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
+      <c r="A30" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="26">
+      <c r="A31" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="28">
         <v>12</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="30">
         <v>1500</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="33">
         <f>IF(OR(C31="",D31=""),"",C31*D31)</f>
       </c>
-      <c r="F31" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="G31" s="31">
+      <c r="F31" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="33">
         <f>IF(E31="","",IF(F31="Yes",E31*(1+GARate),E31))</f>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="39">
         <f>IF(G31="","",G31*(1+FeeRate))</f>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="26">
+      <c r="A32" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="28">
         <v>1</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="30">
         <v>25000</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="33">
         <f>IF(OR(C32="",D32=""),"",C32*D32)</f>
       </c>
-      <c r="F32" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="G32" s="31">
+      <c r="F32" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="33">
         <f>IF(E32="","",IF(F32="Yes",E32*(1+GARate),E32))</f>
       </c>
-      <c r="H32" s="37">
+      <c r="H32" s="39">
         <f>IF(G32="","",G32*(1+FeeRate))</f>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="26">
+      <c r="A33" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="28">
         <v>1</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="30">
         <v>180000</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="33">
         <f>IF(OR(C33="",D33=""),"",C33*D33)</f>
       </c>
-      <c r="F33" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="31">
+      <c r="F33" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="33">
         <f>IF(E33="","",IF(F33="Yes",E33*(1+GARate),E33))</f>
       </c>
-      <c r="H33" s="37">
+      <c r="H33" s="39">
         <f>IF(G33="","",G33*(1+FeeRate))</f>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="31">
+      <c r="A34" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="33">
         <f>IF(OR(C34="",D34=""),"",C34*D34)</f>
       </c>
-      <c r="F34" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="G34" s="31">
+      <c r="F34" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="33">
         <f>IF(E34="","",IF(F34="Yes",E34*(1+GARate),E34))</f>
       </c>
-      <c r="H34" s="37">
+      <c r="H34" s="39">
         <f>IF(G34="","",G34*(1+FeeRate))</f>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="31">
+      <c r="A35" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="33">
         <f>IF(OR(C35="",D35=""),"",C35*D35)</f>
       </c>
-      <c r="F35" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="G35" s="31">
+      <c r="F35" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="33">
         <f>IF(E35="","",IF(F35="Yes",E35*(1+GARate),E35))</f>
       </c>
-      <c r="H35" s="37">
+      <c r="H35" s="39">
         <f>IF(G35="","",G35*(1+FeeRate))</f>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
-        <v>138</v>
+      <c r="A36" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36"/>
-      <c r="G36" s="36">
+      <c r="G36" s="38">
         <f>SUM(G31:G35)</f>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="38">
         <f>SUM(H31:H35)</f>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>139</v>
+      <c r="A38" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="B38"/>
       <c r="C38"/>
@@ -3672,78 +3887,78 @@
       <c r="O38"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>140</v>
+      <c r="A39" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
-      <c r="E39" s="36">
+      <c r="E39" s="38">
         <f>TotalLaborCost</f>
       </c>
       <c r="F39"/>
       <c r="G39"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>141</v>
+      <c r="A40" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
-      <c r="E40" s="36">
+      <c r="E40" s="38">
         <f>TotalODCCost</f>
       </c>
       <c r="F40"/>
       <c r="G40"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>128</v>
+      <c r="A41" s="15" t="s">
+        <v>158</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
-      <c r="E41" s="36">
+      <c r="E41" s="38">
         <f>TotalLaborCost+TotalODCCost</f>
       </c>
       <c r="F41"/>
       <c r="G41"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
-        <v>142</v>
+      <c r="A42" s="15" t="s">
+        <v>167</v>
       </c>
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
-      <c r="E42" s="36">
+      <c r="E42" s="38">
         <f>(TotalLaborCost+TotalODCCost)*FeeRate</f>
       </c>
       <c r="F42"/>
       <c r="G42"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>143</v>
+      <c r="A43" s="15" t="s">
+        <v>168</v>
       </c>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
-      <c r="E43" s="36">
+      <c r="E43" s="38">
         <f>TotalLaborRevenue+TotalODCRevenue</f>
       </c>
       <c r="F43"/>
       <c r="G43"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>144</v>
+      <c r="A44" s="15" t="s">
+        <v>169</v>
       </c>
       <c r="B44"/>
       <c r="C44"/>
       <c r="D44"/>
-      <c r="E44" s="38">
+      <c r="E44" s="40">
         <f>IF((TotalLaborRevenue+TotalODCRevenue)=0,0,((TotalLaborRevenue+TotalODCRevenue)-(TotalLaborCost+TotalODCCost))/(TotalLaborRevenue+TotalODCRevenue))</f>
       </c>
       <c r="F44"/>
@@ -3801,13 +4016,13 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Clearance" error="Use one of the standard clearance levels" sqref="B15:B26">
-      <formula1>"None,Public Trust,Secret,Top Secret,TS/SCI,TS/SCI w/ Poly"</formula1>
+      <formula1>ClearanceLevel</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="ODC category" error="Pick a category" sqref="B31:B35">
-      <formula1>"Materials,Travel,Sub,Equipment,Software,Other"</formula1>
+      <formula1>OdcCategory</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="G&amp;A flag" error="Use Yes or No" sqref="F31:F35">
-      <formula1>"Yes,No"</formula1>
+      <formula1>YesNo</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3819,7 +4034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
@@ -3837,8 +4052,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>145</v>
+      <c r="A1" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -3852,8 +4067,8 @@
       <c r="K1"/>
     </row>
     <row r="2" ht="44" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>146</v>
+      <c r="A2" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -3867,218 +4082,218 @@
       <c r="K2"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="A4" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="41">
+        <v>2.35</v>
+      </c>
+      <c r="E5" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="31">
+        <f>IF(OR(D5="",E5=""),"",80*D5*(1+E5))</f>
+      </c>
+      <c r="G5" s="28">
+        <v>50000</v>
+      </c>
+      <c r="H5" s="39">
+        <f>IF(OR(F5="",G5=""),"",F5*G5)</f>
+      </c>
+      <c r="I5" s="25">
+        <v>12</v>
+      </c>
+      <c r="J5" s="25">
+        <v>5</v>
+      </c>
+      <c r="K5" s="42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="41">
+        <v>2.28</v>
+      </c>
+      <c r="E6" s="21">
+        <v>0.09</v>
+      </c>
+      <c r="F6" s="31">
+        <f>IF(OR(D6="",E6=""),"",80*D6*(1+E6))</f>
+      </c>
+      <c r="G6" s="28">
+        <v>50000</v>
+      </c>
+      <c r="H6" s="39">
+        <f>IF(OR(F6="",G6=""),"",F6*G6)</f>
+      </c>
+      <c r="I6" s="25">
+        <v>8</v>
+      </c>
+      <c r="J6" s="25">
+        <v>4</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="41">
+        <v>1.85</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0.08</v>
+      </c>
+      <c r="F7" s="31">
+        <f>IF(OR(D7="",E7=""),"",80*D7*(1+E7))</f>
+      </c>
+      <c r="G7" s="28">
+        <v>50000</v>
+      </c>
+      <c r="H7" s="39">
+        <f>IF(OR(F7="",G7=""),"",F7*G7)</f>
+      </c>
+      <c r="I7" s="25">
+        <v>5</v>
+      </c>
+      <c r="J7" s="25">
+        <v>4</v>
+      </c>
+      <c r="K7" s="42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="41">
+        <v>1.92</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0.07</v>
+      </c>
+      <c r="F8" s="31">
+        <f>IF(OR(D8="",E8=""),"",80*D8*(1+E8))</f>
+      </c>
+      <c r="G8" s="28">
+        <v>50000</v>
+      </c>
+      <c r="H8" s="39">
+        <f>IF(OR(F8="",G8=""),"",F8*G8)</f>
+      </c>
+      <c r="I8" s="25">
+        <v>3</v>
+      </c>
+      <c r="J8" s="25">
+        <v>3</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="39">
-        <v>2.35</v>
-      </c>
-      <c r="E5" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="29">
-        <f>IF(OR(D5="",E5=""),"",80*D5*(1+E5))</f>
-      </c>
-      <c r="G5" s="26">
-        <v>50000</v>
-      </c>
-      <c r="H5" s="37">
-        <f>IF(OR(F5="",G5=""),"",F5*G5)</f>
-      </c>
-      <c r="I5" s="23">
-        <v>12</v>
-      </c>
-      <c r="J5" s="23">
-        <v>5</v>
-      </c>
-      <c r="K5" s="40" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="39">
-        <v>2.28</v>
-      </c>
-      <c r="E6" s="19">
-        <v>0.09</v>
-      </c>
-      <c r="F6" s="29">
-        <f>IF(OR(D6="",E6=""),"",80*D6*(1+E6))</f>
-      </c>
-      <c r="G6" s="26">
-        <v>50000</v>
-      </c>
-      <c r="H6" s="37">
-        <f>IF(OR(F6="",G6=""),"",F6*G6)</f>
-      </c>
-      <c r="I6" s="23">
-        <v>8</v>
-      </c>
-      <c r="J6" s="23">
-        <v>4</v>
-      </c>
-      <c r="K6" s="40" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" s="39">
-        <v>1.85</v>
-      </c>
-      <c r="E7" s="19">
-        <v>0.08</v>
-      </c>
-      <c r="F7" s="29">
-        <f>IF(OR(D7="",E7=""),"",80*D7*(1+E7))</f>
-      </c>
-      <c r="G7" s="26">
-        <v>50000</v>
-      </c>
-      <c r="H7" s="37">
-        <f>IF(OR(F7="",G7=""),"",F7*G7)</f>
-      </c>
-      <c r="I7" s="23">
-        <v>5</v>
-      </c>
-      <c r="J7" s="23">
-        <v>4</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" s="39">
-        <v>1.92</v>
-      </c>
-      <c r="E8" s="19">
-        <v>0.07</v>
-      </c>
-      <c r="F8" s="29">
-        <f>IF(OR(D8="",E8=""),"",80*D8*(1+E8))</f>
-      </c>
-      <c r="G8" s="26">
-        <v>50000</v>
-      </c>
-      <c r="H8" s="37">
-        <f>IF(OR(F8="",G8=""),"",F8*G8)</f>
-      </c>
-      <c r="I8" s="23">
-        <v>3</v>
-      </c>
-      <c r="J8" s="23">
-        <v>3</v>
-      </c>
-      <c r="K8" s="40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="B9" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" s="31">
         <f>IF(OR(D9="",E9=""),"",80*D9*(1+E9))</f>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="H9" s="37">
+      <c r="G9" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="39">
         <f>IF(OR(F9="",G9=""),"",F9*G9)</f>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>119</v>
+      <c r="I9" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="K9" s="42" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>171</v>
+      <c r="A11" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
@@ -4092,8 +4307,8 @@
       <c r="K11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>172</v>
+      <c r="A12" s="15" t="s">
+        <v>192</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -4101,14 +4316,14 @@
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
-      <c r="H12" s="37">
+      <c r="H12" s="39">
         <f>IFERROR(MIN(H5:H9),0)</f>
       </c>
       <c r="I12"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>173</v>
+      <c r="A13" s="15" t="s">
+        <v>193</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -4116,14 +4331,14 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13" s="37">
+      <c r="H13" s="39">
         <f>IFERROR(MAX(H5:H9),0)</f>
       </c>
       <c r="I13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>174</v>
+      <c r="A14" s="15" t="s">
+        <v>194</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
@@ -4131,14 +4346,14 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
-      <c r="H14" s="37">
+      <c r="H14" s="39">
         <f>IFERROR(MEDIAN(H5:H9),0)</f>
       </c>
       <c r="I14"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>175</v>
+      <c r="A15" s="15" t="s">
+        <v>195</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -4146,14 +4361,14 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
-      <c r="H15" s="37">
+      <c r="H15" s="39">
         <f>IFERROR(AVERAGE(H5:H9),0)</f>
       </c>
       <c r="I15"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>176</v>
+      <c r="A16" s="15" t="s">
+        <v>196</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -4161,14 +4376,14 @@
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
-      <c r="H16" s="21">
+      <c r="H16" s="23">
         <f>IFERROR(AVERAGE(D5:D9),0)</f>
       </c>
       <c r="I16"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>177</v>
+      <c r="A17" s="15" t="s">
+        <v>197</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -4176,7 +4391,7 @@
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
-      <c r="H17" s="41">
+      <c r="H17" s="43">
         <f>COUNTA(A5:A9)</f>
       </c>
       <c r="I17"/>
@@ -4201,10 +4416,10 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="B5:B9">
-      <formula1>"Large,Small,Mid-Size,Unknown"</formula1>
+      <formula1>CompanySize</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="C5:C9">
-      <formula1>"Full &amp; Open,Small Business,8(a),HUBZone,WOSB,EDWOSB,SDVOSB,VOSB"</formula1>
+      <formula1>SetAside</formula1>
     </dataValidation>
     <dataValidation type="whole" showErrorMessage="1" errorStyle="warning" errorTitle="Threat" error="Threat score must be 1-5" sqref="J5:J9">
       <formula1>1</formula1>
@@ -4220,7 +4435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF047857"/>
@@ -4236,8 +4451,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>178</v>
+      <c r="A1" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4246,8 +4461,8 @@
       <c r="F1"/>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>179</v>
+      <c r="A2" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -4256,8 +4471,8 @@
       <c r="F2"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>180</v>
+      <c r="B4" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -4265,99 +4480,99 @@
       <c r="F4"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>182</v>
+      <c r="B5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>201</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="23">
+      <c r="B6" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="25">
         <v>85</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>184</v>
+      <c r="D6" s="22" t="s">
+        <v>203</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="23">
+      <c r="B7" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="25">
         <v>78</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>186</v>
+      <c r="D7" s="22" t="s">
+        <v>205</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="19">
+      <c r="B8" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="21">
         <v>0.55</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>188</v>
+      <c r="D8" s="22" t="s">
+        <v>207</v>
       </c>
       <c r="E8"/>
       <c r="F8"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="C9" s="19">
+      <c r="B9" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="21">
         <v>0.06</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>190</v>
+      <c r="D9" s="22" t="s">
+        <v>209</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="19">
+      <c r="B10" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="21">
         <v>0.08</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>192</v>
+      <c r="D10" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="19">
+      <c r="B11" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="21">
         <v>0.05</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>194</v>
+      <c r="D11" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>195</v>
+      <c r="B13" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C13"/>
       <c r="D13"/>
@@ -4365,144 +4580,144 @@
       <c r="F13"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>200</v>
+      <c r="B14" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="37">
+      <c r="B15" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="39">
         <f>YourProposedPrice*(1-ConsDiscount)</f>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="39">
         <f>YourProposedPrice</f>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="39">
         <f>YourProposedPrice*(1+AggrPremium)</f>
       </c>
-      <c r="F15" s="42" t="s">
-        <v>202</v>
+      <c r="F15" s="44" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="43">
+      <c r="B16" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="45">
         <f>IF(CompMedian=0,"",(C15-CompMedian)/CompMedian)</f>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="45">
         <f>IF(CompMedian=0,"",(D15-CompMedian)/CompMedian)</f>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="45">
         <f>IF(CompMedian=0,"",(E15-CompMedian)/CompMedian)</f>
       </c>
-      <c r="F16" s="42" t="s">
-        <v>204</v>
+      <c r="F16" s="44" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="43">
+      <c r="B17" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="45">
         <f>IF(CompMin=0,"",(C15-CompMin)/CompMin)</f>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="45">
         <f>IF(CompMin=0,"",(D15-CompMin)/CompMin)</f>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="45">
         <f>IF(CompMin=0,"",(E15-CompMin)/CompMin)</f>
       </c>
-      <c r="F17" s="42" t="s">
-        <v>206</v>
+      <c r="F17" s="44" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" s="43">
+      <c r="B18" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="45">
         <f>IF(C15=0,0,(C15-YourTotalCost)/C15)</f>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="45">
         <f>IF(D15=0,0,(D15-YourTotalCost)/D15)</f>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="45">
         <f>IF(E15=0,0,(E15-YourTotalCost)/E15)</f>
       </c>
-      <c r="F18" s="42" t="s">
-        <v>208</v>
+      <c r="F18" s="44" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="37">
+      <c r="B19" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="39">
         <f>C15-YourTotalCost</f>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="39">
         <f>D15-YourTotalCost</f>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="39">
         <f>E15-YourTotalCost</f>
       </c>
-      <c r="F19" s="42" t="s">
-        <v>210</v>
+      <c r="F19" s="44" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="43">
+      <c r="B20" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="45">
         <f>MIN(0.95,MAX(0.05,TargetPWin+0.15+IF(EvalType="Best Value",(YourTechScore-CompTechScore)/200,0)))</f>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="45">
         <f>MIN(0.95,MAX(0.05,TargetPWin+IF(EvalType="Best Value",(YourTechScore-CompTechScore)/200,0)))</f>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="45">
         <f>MIN(0.95,MAX(0.05,TargetPWin-0.12+IF(EvalType="Best Value",(YourTechScore-CompTechScore)/100,0)))</f>
       </c>
-      <c r="F20" s="42" t="s">
-        <v>212</v>
+      <c r="F20" s="44" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C21" s="37">
+      <c r="B21" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="39">
         <f>(C15-YourTotalCost)*C20</f>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="39">
         <f>(D15-YourTotalCost)*D20</f>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="39">
         <f>(E15-YourTotalCost)*E20</f>
       </c>
-      <c r="F21" s="42" t="s">
-        <v>214</v>
+      <c r="F21" s="44" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>215</v>
+      <c r="B23" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C23"/>
       <c r="D23"/>
@@ -4510,28 +4725,28 @@
       <c r="F23"/>
     </row>
     <row r="24" ht="28" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" s="44">
+      <c r="B24" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="46">
         <f>IF(C21=MAX(C21:E21),"Conservative",IF(D21=MAX(C21:E21),"Base","Aggressive"))</f>
       </c>
       <c r="D24"/>
       <c r="E24"/>
     </row>
     <row r="25" ht="28" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C25" s="45">
+      <c r="B25" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="47">
         <f>IF(C24="Conservative",C15,IF(C24="Base",D15,E15))</f>
       </c>
       <c r="D25"/>
       <c r="E25"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>218</v>
+      <c r="B27" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="C27"/>
       <c r="D27"/>
@@ -4539,63 +4754,63 @@
       <c r="F27"/>
     </row>
     <row r="28" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
-        <v>219</v>
+      <c r="B28" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="C28"/>
-      <c r="D28" s="46">
+      <c r="D28" s="48">
         <f>IF(WrapRate&gt;2.5,"FLAG — your wrap exceeds 2.50. Cut overhead before bidding.","OK")</f>
       </c>
       <c r="E28"/>
       <c r="F28"/>
     </row>
     <row r="29" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="s">
-        <v>220</v>
+      <c r="B29" s="15" t="s">
+        <v>239</v>
       </c>
       <c r="C29"/>
-      <c r="D29" s="46">
+      <c r="D29" s="48">
         <f>IF(D18&lt;MinFee,"FLAG — base scenario violates your walk-away margin.","OK")</f>
       </c>
       <c r="E29"/>
       <c r="F29"/>
     </row>
     <row r="30" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
-        <v>221</v>
+      <c r="B30" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="C30"/>
-      <c r="D30" s="46">
+      <c r="D30" s="48">
         <f>IF(CompMin=0,"No competitor data yet",IF((D15-CompMin)/CompMin&gt;0.2,"FLAG — you're 20%+ above lowest bidder. LPTA loss likely.","OK"))</f>
       </c>
       <c r="E30"/>
       <c r="F30"/>
     </row>
     <row r="31" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="s">
-        <v>222</v>
+      <c r="B31" s="15" t="s">
+        <v>241</v>
       </c>
       <c r="C31"/>
-      <c r="D31" s="46">
+      <c r="D31" s="48">
         <f>IF(COUNTA('Competitor Analysis'!A5:A9)=0,"FLAG — fill out Competitor Analysis tab.","OK")</f>
       </c>
       <c r="E31"/>
       <c r="F31"/>
     </row>
     <row r="32" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
-        <v>223</v>
+      <c r="B32" s="15" t="s">
+        <v>242</v>
       </c>
       <c r="C32"/>
-      <c r="D32" s="46">
+      <c r="D32" s="48">
         <f>IF(COUNTIF('Cost Buildup'!O15:O26,"&gt;0.2")+COUNTIF('Cost Buildup'!O15:O26,"&lt;-0.2")&gt;0,"FLAG — at least one labor category is outside the bench band.","OK")</f>
       </c>
       <c r="E32"/>
       <c r="F32"/>
     </row>
     <row r="35" ht="40" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="47" t="s">
-        <v>224</v>
+      <c r="B35" s="49" t="s">
+        <v>243</v>
       </c>
       <c r="C35"/>
       <c r="D35"/>
@@ -4686,7 +4901,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" showErrorMessage="1" sqref="C5">
-      <formula1>"LPTA,Best Value,Tradeoff"</formula1>
+      <formula1>EvalType</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
